--- a/frontend/test_data/header_detection/Wide_Valid_Deep_Junk_Test.xlsx
+++ b/frontend/test_data/header_detection/Wide_Valid_Deep_Junk_Test.xlsx
@@ -15039,7 +15039,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N200"/>
+  <dimension ref="A1:M200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15067,21 +15067,18 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
@@ -15117,15 +15114,12 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M2">
-        <v>46</v>
-      </c>
-      <c r="N2">
         <v>46</v>
       </c>
     </row>
@@ -15161,15 +15155,12 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M3">
-        <v>46</v>
-      </c>
-      <c r="N3">
         <v>46</v>
       </c>
     </row>
@@ -15205,15 +15196,12 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M4">
-        <v>46</v>
-      </c>
-      <c r="N4">
         <v>46</v>
       </c>
     </row>
@@ -15249,15 +15237,12 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M5">
-        <v>46</v>
-      </c>
-      <c r="N5">
         <v>46</v>
       </c>
     </row>
@@ -15293,15 +15278,12 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M6">
-        <v>46</v>
-      </c>
-      <c r="N6">
         <v>46</v>
       </c>
     </row>
@@ -15337,15 +15319,12 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M7">
-        <v>46</v>
-      </c>
-      <c r="N7">
         <v>46</v>
       </c>
     </row>
@@ -15381,15 +15360,12 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M8">
-        <v>46</v>
-      </c>
-      <c r="N8">
         <v>46</v>
       </c>
     </row>
@@ -15425,15 +15401,12 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M9">
-        <v>46</v>
-      </c>
-      <c r="N9">
         <v>46</v>
       </c>
     </row>
@@ -15469,15 +15442,12 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M10">
-        <v>46</v>
-      </c>
-      <c r="N10">
         <v>46</v>
       </c>
     </row>
@@ -15513,15 +15483,12 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M11">
-        <v>46</v>
-      </c>
-      <c r="N11">
         <v>46</v>
       </c>
     </row>
@@ -15557,15 +15524,12 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M12">
-        <v>46</v>
-      </c>
-      <c r="N12">
         <v>46</v>
       </c>
     </row>
@@ -15601,15 +15565,12 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M13">
-        <v>46</v>
-      </c>
-      <c r="N13">
         <v>46</v>
       </c>
     </row>
@@ -15645,15 +15606,12 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M14">
-        <v>46</v>
-      </c>
-      <c r="N14">
         <v>46</v>
       </c>
     </row>
@@ -15689,15 +15647,12 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M15">
-        <v>46</v>
-      </c>
-      <c r="N15">
         <v>46</v>
       </c>
     </row>
@@ -15733,15 +15688,12 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M16">
-        <v>46</v>
-      </c>
-      <c r="N16">
         <v>46</v>
       </c>
     </row>
@@ -15777,15 +15729,12 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M17">
-        <v>46</v>
-      </c>
-      <c r="N17">
         <v>46</v>
       </c>
     </row>
@@ -15821,15 +15770,12 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M18">
-        <v>46</v>
-      </c>
-      <c r="N18">
         <v>46</v>
       </c>
     </row>
@@ -15865,15 +15811,12 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M19">
-        <v>46</v>
-      </c>
-      <c r="N19">
         <v>46</v>
       </c>
     </row>
@@ -15909,15 +15852,12 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M20">
-        <v>46</v>
-      </c>
-      <c r="N20">
         <v>46</v>
       </c>
     </row>
@@ -15953,15 +15893,12 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M21">
-        <v>46</v>
-      </c>
-      <c r="N21">
         <v>46</v>
       </c>
     </row>
@@ -15997,15 +15934,12 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M22">
-        <v>46</v>
-      </c>
-      <c r="N22">
         <v>46</v>
       </c>
     </row>
@@ -16041,15 +15975,12 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M23">
-        <v>46</v>
-      </c>
-      <c r="N23">
         <v>46</v>
       </c>
     </row>
@@ -16085,15 +16016,12 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M24">
-        <v>46</v>
-      </c>
-      <c r="N24">
         <v>46</v>
       </c>
     </row>
@@ -16129,15 +16057,12 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M25">
-        <v>46</v>
-      </c>
-      <c r="N25">
         <v>46</v>
       </c>
     </row>
@@ -16173,15 +16098,12 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M26">
-        <v>46</v>
-      </c>
-      <c r="N26">
         <v>46</v>
       </c>
     </row>
@@ -16217,15 +16139,12 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M27">
-        <v>46</v>
-      </c>
-      <c r="N27">
         <v>46</v>
       </c>
     </row>
@@ -16261,15 +16180,12 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M28">
-        <v>46</v>
-      </c>
-      <c r="N28">
         <v>46</v>
       </c>
     </row>
@@ -16305,15 +16221,12 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M29">
-        <v>46</v>
-      </c>
-      <c r="N29">
         <v>46</v>
       </c>
     </row>
@@ -16349,15 +16262,12 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M30">
-        <v>46</v>
-      </c>
-      <c r="N30">
         <v>46</v>
       </c>
     </row>
@@ -16393,15 +16303,12 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M31">
-        <v>46</v>
-      </c>
-      <c r="N31">
         <v>46</v>
       </c>
     </row>
@@ -16437,15 +16344,12 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L32">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M32">
-        <v>103</v>
-      </c>
-      <c r="N32">
         <v>100</v>
       </c>
     </row>
@@ -16481,15 +16385,12 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L33">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M33">
-        <v>-57</v>
-      </c>
-      <c r="N33">
         <v>0</v>
       </c>
     </row>
@@ -16525,15 +16426,12 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L34">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M34">
-        <v>-57</v>
-      </c>
-      <c r="N34">
         <v>0</v>
       </c>
     </row>
@@ -16569,15 +16467,12 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L35">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M35">
-        <v>-57</v>
-      </c>
-      <c r="N35">
         <v>0</v>
       </c>
     </row>
@@ -16613,15 +16508,12 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L36">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M36">
-        <v>-57</v>
-      </c>
-      <c r="N36">
         <v>0</v>
       </c>
     </row>
@@ -16657,15 +16549,12 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L37">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M37">
-        <v>-57</v>
-      </c>
-      <c r="N37">
         <v>0</v>
       </c>
     </row>
@@ -16701,15 +16590,12 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L38">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M38">
-        <v>-57</v>
-      </c>
-      <c r="N38">
         <v>0</v>
       </c>
     </row>
@@ -16745,15 +16631,12 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L39">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M39">
-        <v>-57</v>
-      </c>
-      <c r="N39">
         <v>0</v>
       </c>
     </row>
@@ -16789,15 +16672,12 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L40">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M40">
-        <v>-57</v>
-      </c>
-      <c r="N40">
         <v>0</v>
       </c>
     </row>
@@ -16833,15 +16713,12 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L41">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M41">
-        <v>-57</v>
-      </c>
-      <c r="N41">
         <v>0</v>
       </c>
     </row>
@@ -16877,15 +16754,12 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L42">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M42">
-        <v>-57</v>
-      </c>
-      <c r="N42">
         <v>0</v>
       </c>
     </row>
@@ -16921,15 +16795,12 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L43">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M43">
-        <v>-57</v>
-      </c>
-      <c r="N43">
         <v>0</v>
       </c>
     </row>
@@ -16965,15 +16836,12 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L44">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M44">
-        <v>-57</v>
-      </c>
-      <c r="N44">
         <v>0</v>
       </c>
     </row>
@@ -17009,15 +16877,12 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L45">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M45">
-        <v>-57</v>
-      </c>
-      <c r="N45">
         <v>0</v>
       </c>
     </row>
@@ -17053,15 +16918,12 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L46">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M46">
-        <v>-57</v>
-      </c>
-      <c r="N46">
         <v>0</v>
       </c>
     </row>
@@ -17097,15 +16959,12 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L47">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M47">
-        <v>-57</v>
-      </c>
-      <c r="N47">
         <v>0</v>
       </c>
     </row>
@@ -17141,15 +17000,12 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L48">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M48">
-        <v>-57</v>
-      </c>
-      <c r="N48">
         <v>0</v>
       </c>
     </row>
@@ -17185,15 +17041,12 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L49">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M49">
-        <v>-57</v>
-      </c>
-      <c r="N49">
         <v>0</v>
       </c>
     </row>
@@ -17229,15 +17082,12 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L50">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M50">
-        <v>-57</v>
-      </c>
-      <c r="N50">
         <v>0</v>
       </c>
     </row>
@@ -17273,15 +17123,12 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L51">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M51">
-        <v>-57</v>
-      </c>
-      <c r="N51">
         <v>0</v>
       </c>
     </row>
@@ -17317,15 +17164,12 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L52">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M52">
-        <v>-57</v>
-      </c>
-      <c r="N52">
         <v>0</v>
       </c>
     </row>
@@ -17361,15 +17205,12 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L53">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M53">
-        <v>-57</v>
-      </c>
-      <c r="N53">
         <v>0</v>
       </c>
     </row>
@@ -17405,15 +17246,12 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L54">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M54">
-        <v>-57</v>
-      </c>
-      <c r="N54">
         <v>0</v>
       </c>
     </row>
@@ -17449,15 +17287,12 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L55">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M55">
-        <v>-57</v>
-      </c>
-      <c r="N55">
         <v>0</v>
       </c>
     </row>
@@ -17493,15 +17328,12 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L56">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M56">
-        <v>-57</v>
-      </c>
-      <c r="N56">
         <v>0</v>
       </c>
     </row>
@@ -17537,15 +17369,12 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L57">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M57">
-        <v>-57</v>
-      </c>
-      <c r="N57">
         <v>0</v>
       </c>
     </row>
@@ -17581,15 +17410,12 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L58">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M58">
-        <v>-57</v>
-      </c>
-      <c r="N58">
         <v>0</v>
       </c>
     </row>
@@ -17625,15 +17451,12 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L59">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M59">
-        <v>-57</v>
-      </c>
-      <c r="N59">
         <v>0</v>
       </c>
     </row>
@@ -17669,15 +17492,12 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L60">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M60">
-        <v>-57</v>
-      </c>
-      <c r="N60">
         <v>0</v>
       </c>
     </row>
@@ -17713,15 +17533,12 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L61">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M61">
-        <v>-57</v>
-      </c>
-      <c r="N61">
         <v>0</v>
       </c>
     </row>
@@ -17757,15 +17574,12 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L62">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M62">
-        <v>-57</v>
-      </c>
-      <c r="N62">
         <v>0</v>
       </c>
     </row>
@@ -17801,15 +17615,12 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L63">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M63">
-        <v>-57</v>
-      </c>
-      <c r="N63">
         <v>0</v>
       </c>
     </row>
@@ -17845,15 +17656,12 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L64">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M64">
-        <v>-57</v>
-      </c>
-      <c r="N64">
         <v>0</v>
       </c>
     </row>
@@ -17889,15 +17697,12 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L65">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M65">
-        <v>-57</v>
-      </c>
-      <c r="N65">
         <v>0</v>
       </c>
     </row>
@@ -17933,15 +17738,12 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L66">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M66">
-        <v>-57</v>
-      </c>
-      <c r="N66">
         <v>0</v>
       </c>
     </row>
@@ -17977,15 +17779,12 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L67">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M67">
-        <v>-57</v>
-      </c>
-      <c r="N67">
         <v>0</v>
       </c>
     </row>
@@ -18021,15 +17820,12 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L68">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M68">
-        <v>-57</v>
-      </c>
-      <c r="N68">
         <v>0</v>
       </c>
     </row>
@@ -18065,15 +17861,12 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L69">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M69">
-        <v>-57</v>
-      </c>
-      <c r="N69">
         <v>0</v>
       </c>
     </row>
@@ -18109,15 +17902,12 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L70">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M70">
-        <v>-57</v>
-      </c>
-      <c r="N70">
         <v>0</v>
       </c>
     </row>
@@ -18153,15 +17943,12 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L71">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M71">
-        <v>-57</v>
-      </c>
-      <c r="N71">
         <v>0</v>
       </c>
     </row>
@@ -18197,15 +17984,12 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L72">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M72">
-        <v>-57</v>
-      </c>
-      <c r="N72">
         <v>0</v>
       </c>
     </row>
@@ -18241,15 +18025,12 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L73">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M73">
-        <v>-57</v>
-      </c>
-      <c r="N73">
         <v>0</v>
       </c>
     </row>
@@ -18285,15 +18066,12 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L74">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M74">
-        <v>-57</v>
-      </c>
-      <c r="N74">
         <v>0</v>
       </c>
     </row>
@@ -18329,15 +18107,12 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L75">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M75">
-        <v>-57</v>
-      </c>
-      <c r="N75">
         <v>0</v>
       </c>
     </row>
@@ -18373,15 +18148,12 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L76">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M76">
-        <v>-57</v>
-      </c>
-      <c r="N76">
         <v>0</v>
       </c>
     </row>
@@ -18417,15 +18189,12 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L77">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M77">
-        <v>-57</v>
-      </c>
-      <c r="N77">
         <v>0</v>
       </c>
     </row>
@@ -18461,15 +18230,12 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L78">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M78">
-        <v>-57</v>
-      </c>
-      <c r="N78">
         <v>0</v>
       </c>
     </row>
@@ -18505,15 +18271,12 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L79">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M79">
-        <v>-57</v>
-      </c>
-      <c r="N79">
         <v>0</v>
       </c>
     </row>
@@ -18549,15 +18312,12 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L80">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M80">
-        <v>-57</v>
-      </c>
-      <c r="N80">
         <v>0</v>
       </c>
     </row>
@@ -18593,15 +18353,12 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L81">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M81">
-        <v>-57</v>
-      </c>
-      <c r="N81">
         <v>0</v>
       </c>
     </row>
@@ -18637,15 +18394,12 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L82">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M82">
-        <v>-57</v>
-      </c>
-      <c r="N82">
         <v>0</v>
       </c>
     </row>
@@ -18681,15 +18435,12 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L83">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M83">
-        <v>-57</v>
-      </c>
-      <c r="N83">
         <v>0</v>
       </c>
     </row>
@@ -18725,15 +18476,12 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L84">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M84">
-        <v>-57</v>
-      </c>
-      <c r="N84">
         <v>0</v>
       </c>
     </row>
@@ -18769,15 +18517,12 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L85">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M85">
-        <v>-57</v>
-      </c>
-      <c r="N85">
         <v>0</v>
       </c>
     </row>
@@ -18813,15 +18558,12 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L86">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M86">
-        <v>-57</v>
-      </c>
-      <c r="N86">
         <v>0</v>
       </c>
     </row>
@@ -18857,15 +18599,12 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L87">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M87">
-        <v>-57</v>
-      </c>
-      <c r="N87">
         <v>0</v>
       </c>
     </row>
@@ -18901,15 +18640,12 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L88">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M88">
-        <v>-57</v>
-      </c>
-      <c r="N88">
         <v>0</v>
       </c>
     </row>
@@ -18945,15 +18681,12 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L89">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M89">
-        <v>-57</v>
-      </c>
-      <c r="N89">
         <v>0</v>
       </c>
     </row>
@@ -18989,15 +18722,12 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L90">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M90">
-        <v>-57</v>
-      </c>
-      <c r="N90">
         <v>0</v>
       </c>
     </row>
@@ -19033,15 +18763,12 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L91">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M91">
-        <v>-57</v>
-      </c>
-      <c r="N91">
         <v>0</v>
       </c>
     </row>
@@ -19077,15 +18804,12 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L92">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M92">
-        <v>-57</v>
-      </c>
-      <c r="N92">
         <v>0</v>
       </c>
     </row>
@@ -19121,15 +18845,12 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L93">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M93">
-        <v>-57</v>
-      </c>
-      <c r="N93">
         <v>0</v>
       </c>
     </row>
@@ -19165,15 +18886,12 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L94">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M94">
-        <v>-57</v>
-      </c>
-      <c r="N94">
         <v>0</v>
       </c>
     </row>
@@ -19209,15 +18927,12 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L95">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M95">
-        <v>-57</v>
-      </c>
-      <c r="N95">
         <v>0</v>
       </c>
     </row>
@@ -19253,15 +18968,12 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L96">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M96">
-        <v>-57</v>
-      </c>
-      <c r="N96">
         <v>0</v>
       </c>
     </row>
@@ -19297,15 +19009,12 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L97">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M97">
-        <v>-57</v>
-      </c>
-      <c r="N97">
         <v>0</v>
       </c>
     </row>
@@ -19341,15 +19050,12 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L98">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M98">
-        <v>-57</v>
-      </c>
-      <c r="N98">
         <v>0</v>
       </c>
     </row>
@@ -19385,15 +19091,12 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L99">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M99">
-        <v>-57</v>
-      </c>
-      <c r="N99">
         <v>0</v>
       </c>
     </row>
@@ -19429,15 +19132,12 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L100">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M100">
-        <v>-57</v>
-      </c>
-      <c r="N100">
         <v>0</v>
       </c>
     </row>
@@ -19473,15 +19173,12 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L101">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M101">
-        <v>-57</v>
-      </c>
-      <c r="N101">
         <v>0</v>
       </c>
     </row>
@@ -19517,15 +19214,12 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L102">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M102">
-        <v>-57</v>
-      </c>
-      <c r="N102">
         <v>0</v>
       </c>
     </row>
@@ -19561,15 +19255,12 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L103">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M103">
-        <v>-57</v>
-      </c>
-      <c r="N103">
         <v>0</v>
       </c>
     </row>
@@ -19605,15 +19296,12 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L104">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M104">
-        <v>-57</v>
-      </c>
-      <c r="N104">
         <v>0</v>
       </c>
     </row>
@@ -19649,15 +19337,12 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L105">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M105">
-        <v>-57</v>
-      </c>
-      <c r="N105">
         <v>0</v>
       </c>
     </row>
@@ -19693,15 +19378,12 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L106">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M106">
-        <v>-57</v>
-      </c>
-      <c r="N106">
         <v>0</v>
       </c>
     </row>
@@ -19737,15 +19419,12 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L107">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M107">
-        <v>-57</v>
-      </c>
-      <c r="N107">
         <v>0</v>
       </c>
     </row>
@@ -19781,15 +19460,12 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L108">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M108">
-        <v>-57</v>
-      </c>
-      <c r="N108">
         <v>0</v>
       </c>
     </row>
@@ -19825,15 +19501,12 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L109">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M109">
-        <v>-57</v>
-      </c>
-      <c r="N109">
         <v>0</v>
       </c>
     </row>
@@ -19869,15 +19542,12 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L110">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M110">
-        <v>-57</v>
-      </c>
-      <c r="N110">
         <v>0</v>
       </c>
     </row>
@@ -19913,15 +19583,12 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L111">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M111">
-        <v>-57</v>
-      </c>
-      <c r="N111">
         <v>0</v>
       </c>
     </row>
@@ -19957,15 +19624,12 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L112">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M112">
-        <v>-57</v>
-      </c>
-      <c r="N112">
         <v>0</v>
       </c>
     </row>
@@ -20001,15 +19665,12 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L113">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M113">
-        <v>-57</v>
-      </c>
-      <c r="N113">
         <v>0</v>
       </c>
     </row>
@@ -20045,15 +19706,12 @@
         <v>0</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L114">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M114">
-        <v>-57</v>
-      </c>
-      <c r="N114">
         <v>0</v>
       </c>
     </row>
@@ -20089,15 +19747,12 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L115">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M115">
-        <v>-57</v>
-      </c>
-      <c r="N115">
         <v>0</v>
       </c>
     </row>
@@ -20133,15 +19788,12 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L116">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M116">
-        <v>-57</v>
-      </c>
-      <c r="N116">
         <v>0</v>
       </c>
     </row>
@@ -20177,15 +19829,12 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L117">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M117">
-        <v>-57</v>
-      </c>
-      <c r="N117">
         <v>0</v>
       </c>
     </row>
@@ -20221,15 +19870,12 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L118">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M118">
-        <v>-57</v>
-      </c>
-      <c r="N118">
         <v>0</v>
       </c>
     </row>
@@ -20265,15 +19911,12 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L119">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M119">
-        <v>-57</v>
-      </c>
-      <c r="N119">
         <v>0</v>
       </c>
     </row>
@@ -20309,15 +19952,12 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L120">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M120">
-        <v>-57</v>
-      </c>
-      <c r="N120">
         <v>0</v>
       </c>
     </row>
@@ -20353,15 +19993,12 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L121">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M121">
-        <v>-57</v>
-      </c>
-      <c r="N121">
         <v>0</v>
       </c>
     </row>
@@ -20397,15 +20034,12 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L122">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M122">
-        <v>-57</v>
-      </c>
-      <c r="N122">
         <v>0</v>
       </c>
     </row>
@@ -20441,15 +20075,12 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L123">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M123">
-        <v>-57</v>
-      </c>
-      <c r="N123">
         <v>0</v>
       </c>
     </row>
@@ -20485,15 +20116,12 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L124">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M124">
-        <v>-57</v>
-      </c>
-      <c r="N124">
         <v>0</v>
       </c>
     </row>
@@ -20529,15 +20157,12 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L125">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M125">
-        <v>-57</v>
-      </c>
-      <c r="N125">
         <v>0</v>
       </c>
     </row>
@@ -20573,15 +20198,12 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L126">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M126">
-        <v>-57</v>
-      </c>
-      <c r="N126">
         <v>0</v>
       </c>
     </row>
@@ -20617,15 +20239,12 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L127">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M127">
-        <v>-57</v>
-      </c>
-      <c r="N127">
         <v>0</v>
       </c>
     </row>
@@ -20661,15 +20280,12 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L128">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M128">
-        <v>-57</v>
-      </c>
-      <c r="N128">
         <v>0</v>
       </c>
     </row>
@@ -20705,15 +20321,12 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L129">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M129">
-        <v>-57</v>
-      </c>
-      <c r="N129">
         <v>0</v>
       </c>
     </row>
@@ -20749,15 +20362,12 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L130">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M130">
-        <v>-57</v>
-      </c>
-      <c r="N130">
         <v>0</v>
       </c>
     </row>
@@ -20793,15 +20403,12 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L131">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M131">
-        <v>-57</v>
-      </c>
-      <c r="N131">
         <v>0</v>
       </c>
     </row>
@@ -20837,15 +20444,12 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L132">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M132">
-        <v>-57</v>
-      </c>
-      <c r="N132">
         <v>0</v>
       </c>
     </row>
@@ -20881,15 +20485,12 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L133">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M133">
-        <v>-57</v>
-      </c>
-      <c r="N133">
         <v>0</v>
       </c>
     </row>
@@ -20925,15 +20526,12 @@
         <v>0</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L134">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M134">
-        <v>-57</v>
-      </c>
-      <c r="N134">
         <v>0</v>
       </c>
     </row>
@@ -20969,15 +20567,12 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L135">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M135">
-        <v>-57</v>
-      </c>
-      <c r="N135">
         <v>0</v>
       </c>
     </row>
@@ -21013,15 +20608,12 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L136">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M136">
-        <v>-57</v>
-      </c>
-      <c r="N136">
         <v>0</v>
       </c>
     </row>
@@ -21057,15 +20649,12 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L137">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M137">
-        <v>-57</v>
-      </c>
-      <c r="N137">
         <v>0</v>
       </c>
     </row>
@@ -21101,15 +20690,12 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L138">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M138">
-        <v>-57</v>
-      </c>
-      <c r="N138">
         <v>0</v>
       </c>
     </row>
@@ -21145,15 +20731,12 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L139">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M139">
-        <v>-57</v>
-      </c>
-      <c r="N139">
         <v>0</v>
       </c>
     </row>
@@ -21189,15 +20772,12 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L140">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M140">
-        <v>-57</v>
-      </c>
-      <c r="N140">
         <v>0</v>
       </c>
     </row>
@@ -21233,15 +20813,12 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L141">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M141">
-        <v>-57</v>
-      </c>
-      <c r="N141">
         <v>0</v>
       </c>
     </row>
@@ -21277,15 +20854,12 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L142">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M142">
-        <v>-57</v>
-      </c>
-      <c r="N142">
         <v>0</v>
       </c>
     </row>
@@ -21321,15 +20895,12 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L143">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M143">
-        <v>-57</v>
-      </c>
-      <c r="N143">
         <v>0</v>
       </c>
     </row>
@@ -21365,15 +20936,12 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L144">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M144">
-        <v>-57</v>
-      </c>
-      <c r="N144">
         <v>0</v>
       </c>
     </row>
@@ -21409,15 +20977,12 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L145">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M145">
-        <v>-57</v>
-      </c>
-      <c r="N145">
         <v>0</v>
       </c>
     </row>
@@ -21453,15 +21018,12 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L146">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M146">
-        <v>-57</v>
-      </c>
-      <c r="N146">
         <v>0</v>
       </c>
     </row>
@@ -21497,15 +21059,12 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L147">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M147">
-        <v>-57</v>
-      </c>
-      <c r="N147">
         <v>0</v>
       </c>
     </row>
@@ -21541,15 +21100,12 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L148">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M148">
-        <v>-57</v>
-      </c>
-      <c r="N148">
         <v>0</v>
       </c>
     </row>
@@ -21585,15 +21141,12 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L149">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M149">
-        <v>-57</v>
-      </c>
-      <c r="N149">
         <v>0</v>
       </c>
     </row>
@@ -21629,15 +21182,12 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L150">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M150">
-        <v>-57</v>
-      </c>
-      <c r="N150">
         <v>0</v>
       </c>
     </row>
@@ -21673,15 +21223,12 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L151">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M151">
-        <v>-57</v>
-      </c>
-      <c r="N151">
         <v>0</v>
       </c>
     </row>
@@ -21717,15 +21264,12 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L152">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M152">
-        <v>-57</v>
-      </c>
-      <c r="N152">
         <v>0</v>
       </c>
     </row>
@@ -21761,15 +21305,12 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L153">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M153">
-        <v>-57</v>
-      </c>
-      <c r="N153">
         <v>0</v>
       </c>
     </row>
@@ -21805,15 +21346,12 @@
         <v>0</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L154">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M154">
-        <v>-57</v>
-      </c>
-      <c r="N154">
         <v>0</v>
       </c>
     </row>
@@ -21849,15 +21387,12 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L155">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M155">
-        <v>-57</v>
-      </c>
-      <c r="N155">
         <v>0</v>
       </c>
     </row>
@@ -21893,15 +21428,12 @@
         <v>0</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L156">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M156">
-        <v>-57</v>
-      </c>
-      <c r="N156">
         <v>0</v>
       </c>
     </row>
@@ -21937,15 +21469,12 @@
         <v>0</v>
       </c>
       <c r="K157">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L157">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M157">
-        <v>-57</v>
-      </c>
-      <c r="N157">
         <v>0</v>
       </c>
     </row>
@@ -21981,15 +21510,12 @@
         <v>0</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L158">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M158">
-        <v>-57</v>
-      </c>
-      <c r="N158">
         <v>0</v>
       </c>
     </row>
@@ -22025,15 +21551,12 @@
         <v>0</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L159">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M159">
-        <v>-57</v>
-      </c>
-      <c r="N159">
         <v>0</v>
       </c>
     </row>
@@ -22069,15 +21592,12 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L160">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M160">
-        <v>-57</v>
-      </c>
-      <c r="N160">
         <v>0</v>
       </c>
     </row>
@@ -22113,15 +21633,12 @@
         <v>0</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L161">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M161">
-        <v>-57</v>
-      </c>
-      <c r="N161">
         <v>0</v>
       </c>
     </row>
@@ -22157,15 +21674,12 @@
         <v>0</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L162">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M162">
-        <v>-57</v>
-      </c>
-      <c r="N162">
         <v>0</v>
       </c>
     </row>
@@ -22201,15 +21715,12 @@
         <v>0</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L163">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M163">
-        <v>-57</v>
-      </c>
-      <c r="N163">
         <v>0</v>
       </c>
     </row>
@@ -22245,15 +21756,12 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L164">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M164">
-        <v>-57</v>
-      </c>
-      <c r="N164">
         <v>0</v>
       </c>
     </row>
@@ -22289,15 +21797,12 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L165">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M165">
-        <v>-57</v>
-      </c>
-      <c r="N165">
         <v>0</v>
       </c>
     </row>
@@ -22333,15 +21838,12 @@
         <v>0</v>
       </c>
       <c r="K166">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L166">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M166">
-        <v>-57</v>
-      </c>
-      <c r="N166">
         <v>0</v>
       </c>
     </row>
@@ -22377,15 +21879,12 @@
         <v>0</v>
       </c>
       <c r="K167">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L167">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M167">
-        <v>-57</v>
-      </c>
-      <c r="N167">
         <v>0</v>
       </c>
     </row>
@@ -22421,15 +21920,12 @@
         <v>0</v>
       </c>
       <c r="K168">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L168">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M168">
-        <v>-57</v>
-      </c>
-      <c r="N168">
         <v>0</v>
       </c>
     </row>
@@ -22465,15 +21961,12 @@
         <v>0</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L169">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M169">
-        <v>-57</v>
-      </c>
-      <c r="N169">
         <v>0</v>
       </c>
     </row>
@@ -22509,15 +22002,12 @@
         <v>0</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L170">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M170">
-        <v>-57</v>
-      </c>
-      <c r="N170">
         <v>0</v>
       </c>
     </row>
@@ -22553,15 +22043,12 @@
         <v>0</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L171">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M171">
-        <v>-57</v>
-      </c>
-      <c r="N171">
         <v>0</v>
       </c>
     </row>
@@ -22597,15 +22084,12 @@
         <v>0</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L172">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M172">
-        <v>-57</v>
-      </c>
-      <c r="N172">
         <v>0</v>
       </c>
     </row>
@@ -22641,15 +22125,12 @@
         <v>0</v>
       </c>
       <c r="K173">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L173">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M173">
-        <v>-57</v>
-      </c>
-      <c r="N173">
         <v>0</v>
       </c>
     </row>
@@ -22685,15 +22166,12 @@
         <v>0</v>
       </c>
       <c r="K174">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L174">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M174">
-        <v>-57</v>
-      </c>
-      <c r="N174">
         <v>0</v>
       </c>
     </row>
@@ -22729,15 +22207,12 @@
         <v>0</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L175">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M175">
-        <v>-57</v>
-      </c>
-      <c r="N175">
         <v>0</v>
       </c>
     </row>
@@ -22773,15 +22248,12 @@
         <v>0</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L176">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M176">
-        <v>-57</v>
-      </c>
-      <c r="N176">
         <v>0</v>
       </c>
     </row>
@@ -22817,15 +22289,12 @@
         <v>0</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L177">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M177">
-        <v>-57</v>
-      </c>
-      <c r="N177">
         <v>0</v>
       </c>
     </row>
@@ -22861,15 +22330,12 @@
         <v>0</v>
       </c>
       <c r="K178">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L178">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M178">
-        <v>-57</v>
-      </c>
-      <c r="N178">
         <v>0</v>
       </c>
     </row>
@@ -22905,15 +22371,12 @@
         <v>0</v>
       </c>
       <c r="K179">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L179">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M179">
-        <v>-57</v>
-      </c>
-      <c r="N179">
         <v>0</v>
       </c>
     </row>
@@ -22949,15 +22412,12 @@
         <v>0</v>
       </c>
       <c r="K180">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L180">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M180">
-        <v>-57</v>
-      </c>
-      <c r="N180">
         <v>0</v>
       </c>
     </row>
@@ -22993,15 +22453,12 @@
         <v>0</v>
       </c>
       <c r="K181">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L181">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M181">
-        <v>-57</v>
-      </c>
-      <c r="N181">
         <v>0</v>
       </c>
     </row>
@@ -23037,15 +22494,12 @@
         <v>0</v>
       </c>
       <c r="K182">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L182">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M182">
-        <v>-57</v>
-      </c>
-      <c r="N182">
         <v>0</v>
       </c>
     </row>
@@ -23081,15 +22535,12 @@
         <v>0</v>
       </c>
       <c r="K183">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L183">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M183">
-        <v>-57</v>
-      </c>
-      <c r="N183">
         <v>0</v>
       </c>
     </row>
@@ -23125,15 +22576,12 @@
         <v>0</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L184">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M184">
-        <v>-57</v>
-      </c>
-      <c r="N184">
         <v>0</v>
       </c>
     </row>
@@ -23169,15 +22617,12 @@
         <v>0</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L185">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M185">
-        <v>-57</v>
-      </c>
-      <c r="N185">
         <v>0</v>
       </c>
     </row>
@@ -23213,15 +22658,12 @@
         <v>0</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L186">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M186">
-        <v>-57</v>
-      </c>
-      <c r="N186">
         <v>0</v>
       </c>
     </row>
@@ -23257,15 +22699,12 @@
         <v>0</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L187">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M187">
-        <v>-57</v>
-      </c>
-      <c r="N187">
         <v>0</v>
       </c>
     </row>
@@ -23301,15 +22740,12 @@
         <v>0</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L188">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M188">
-        <v>-57</v>
-      </c>
-      <c r="N188">
         <v>0</v>
       </c>
     </row>
@@ -23345,15 +22781,12 @@
         <v>0</v>
       </c>
       <c r="K189">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L189">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M189">
-        <v>-57</v>
-      </c>
-      <c r="N189">
         <v>0</v>
       </c>
     </row>
@@ -23389,15 +22822,12 @@
         <v>0</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L190">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M190">
-        <v>-57</v>
-      </c>
-      <c r="N190">
         <v>0</v>
       </c>
     </row>
@@ -23433,15 +22863,12 @@
         <v>0</v>
       </c>
       <c r="K191">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L191">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M191">
-        <v>-57</v>
-      </c>
-      <c r="N191">
         <v>0</v>
       </c>
     </row>
@@ -23477,15 +22904,12 @@
         <v>0</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L192">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M192">
-        <v>-57</v>
-      </c>
-      <c r="N192">
         <v>0</v>
       </c>
     </row>
@@ -23518,18 +22942,15 @@
         <v>0</v>
       </c>
       <c r="J193">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K193">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L193">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M193">
-        <v>-67</v>
-      </c>
-      <c r="N193">
         <v>0</v>
       </c>
     </row>
@@ -23562,18 +22983,15 @@
         <v>0</v>
       </c>
       <c r="J194">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K194">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L194">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M194">
-        <v>-67</v>
-      </c>
-      <c r="N194">
         <v>0</v>
       </c>
     </row>
@@ -23606,18 +23024,15 @@
         <v>0</v>
       </c>
       <c r="J195">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K195">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L195">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M195">
-        <v>-67</v>
-      </c>
-      <c r="N195">
         <v>0</v>
       </c>
     </row>
@@ -23650,18 +23065,15 @@
         <v>0</v>
       </c>
       <c r="J196">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K196">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L196">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M196">
-        <v>-67</v>
-      </c>
-      <c r="N196">
         <v>0</v>
       </c>
     </row>
@@ -23694,18 +23106,15 @@
         <v>0</v>
       </c>
       <c r="J197">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K197">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L197">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M197">
-        <v>-67</v>
-      </c>
-      <c r="N197">
         <v>0</v>
       </c>
     </row>
@@ -23738,18 +23147,15 @@
         <v>0</v>
       </c>
       <c r="J198">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K198">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L198">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M198">
-        <v>-67</v>
-      </c>
-      <c r="N198">
         <v>0</v>
       </c>
     </row>
@@ -23782,18 +23188,15 @@
         <v>0</v>
       </c>
       <c r="J199">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K199">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L199">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M199">
-        <v>-67</v>
-      </c>
-      <c r="N199">
         <v>0</v>
       </c>
     </row>
@@ -23826,24 +23229,21 @@
         <v>0</v>
       </c>
       <c r="J200">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K200">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L200">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M200">
-        <v>-67</v>
-      </c>
-      <c r="N200">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M200"/>
   </ignoredErrors>
 </worksheet>
 </file>